--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>132857485</v>
       </c>
       <c r="B3" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>132857485</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132857735</v>
       </c>
       <c r="B2" t="n">
-        <v>57954</v>
+        <v>57957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132857485</v>
       </c>
       <c r="B3" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132857708</v>
       </c>
       <c r="B4" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>132857485</v>
       </c>
       <c r="B3" t="n">
-        <v>91916</v>
+        <v>91917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132857735</v>
       </c>
       <c r="B2" t="n">
-        <v>57957</v>
+        <v>57958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132857485</v>
       </c>
       <c r="B3" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132857708</v>
       </c>
       <c r="B4" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132857735</v>
+        <v>132857469</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hamrekröken, Hamrekröken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557093</v>
+        <v>557116</v>
       </c>
       <c r="R2" t="n">
-        <v>6685720</v>
+        <v>6685686</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132857485</v>
+        <v>132857467</v>
       </c>
       <c r="B3" t="n">
-        <v>91920</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557116</v>
+        <v>557114</v>
       </c>
       <c r="R3" t="n">
-        <v>6685686</v>
+        <v>6685682</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,40 +869,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132857708</v>
+        <v>132857579</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hamrekröken, Hamrekröken, Dlr</t>
@@ -973,6 +963,210 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132857708</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hamrekröken, Hamrekröken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557109</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685724</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132857735</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hamrekröken, Hamrekröken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557093</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685720</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5326-2026 artfynd.xlsx
+++ b/artfynd/A 5326-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132857469</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132857467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132857579</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132857708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132857735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>